--- a/artfynd/A 17694-2026 artfynd.xlsx
+++ b/artfynd/A 17694-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75541608</v>
+        <v>6776429</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,20 +703,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stenfjärden, Upl</t>
+          <t>Stenskär, västra delen, nordsidan av vägen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>682320.4927697368</v>
+        <v>682156</v>
       </c>
       <c r="R2" t="n">
-        <v>6694942.723914813</v>
+        <v>6694919</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,24 +747,24 @@
           <t>Börstil</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>C-Öst-0759</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-09-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-09-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>3 m N om vägbanan 12 ex med 19 blommor, norra vägslänten 1 ex med 2 blommor</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +779,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Jakobsson</t>
+          <t>Floraväkterisamordn C-län</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Jakobsson, Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Ebbe Zachrisson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>75541607</v>
       </c>
       <c r="B3" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>682306.7582764989</v>
+        <v>682307</v>
       </c>
       <c r="R3" t="n">
-        <v>6694820.569501891</v>
+        <v>6694821</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -864,19 +867,9 @@
           <t>2018-09-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-09-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,6 +894,215 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>75541608</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stenfjärden, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>682320</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6694943</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-09-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-09-19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Maria Jakobsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Maria Jakobsson, Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>86885042</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99803</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222322</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ängsstarr</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carex hostiana</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bolhamnsänden, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>682398</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6694922</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-07-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-07-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Större bestånd</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Extremrikkärr</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sebastian Sundberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sebastian Sundberg, Karl Soler Kinnerbäck, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17694-2026 artfynd.xlsx
+++ b/artfynd/A 17694-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6776429</t>
         </is>
       </c>
     </row>
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75541607</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75541608</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,8 +1123,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86885042</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>